--- a/backend/data/contest.xlsx
+++ b/backend/data/contest.xlsx
@@ -1,440 +1,129 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="users" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="problems" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="contests" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="contest_problems" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="submissions" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="leaderboard" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="sessions" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="users" sheetId="1" r:id="rId1"/>
+    <sheet name="problems" sheetId="2" r:id="rId2"/>
+    <sheet name="contests" sheetId="3" r:id="rId3"/>
+    <sheet name="contest_problems" sheetId="4" r:id="rId4"/>
+    <sheet name="submissions" sheetId="5" r:id="rId5"/>
+    <sheet name="leaderboard" sheetId="6" r:id="rId6"/>
+    <sheet name="sessions" sheetId="7" r:id="rId7"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <name val="Calibri"/>
+      <sz val="10"/>
+      <color rgb="FF0F172A"/>
+      <name val="Segoe UI"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="007C3AED"/>
+        <fgColor rgb="FF312E81"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8FAFC"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE2E8F0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE2E8F0"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+  <cellXfs count="10">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
-</file>
-
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="1F497D"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="EEECE1"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="4F81BD"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="C0504D"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="9BBB59"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="8064A2"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="4BACC6"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="F79646"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0000FF"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="800080"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="40000">
-              <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-</a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:H3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="40" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="25" customWidth="1"/>
+    <col min="4" max="4" width="40" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="7" max="7" width="31" customWidth="1"/>
+    <col min="8" max="8" width="17" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>id</t>
@@ -476,101 +165,114 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>7468653e-dfa4-492c-923f-1891feb76181</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>admin</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>admin@codearena.io</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>15640d7f5fecd44797b8ebf3df1c8390a30a29b44f7d625f8027c1e4c534b778</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>admin</t>
         </is>
       </c>
-      <c r="F2" t="n">
+      <c r="F2" s="7">
         <v>2500</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>2026-10-11T18:37:21.899197</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>#7c3aed</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>216bb78f-92ec-46cb-a033-85bd1a01496e</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>ZaHeDuL</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>zizahed202@gmail.com</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>bc7d5b451effec0ae361f2532ec3bed5167839e0a1ec213e9e8faac41c604c9d</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>user</t>
         </is>
       </c>
-      <c r="F3" t="n">
+      <c r="F3" s="6">
         <v>1200</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>2026-10-11T18:48:03.939063</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>#06b6d4</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <autoFilter ref="A1:H3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:P6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="40" customWidth="1"/>
+    <col min="2" max="2" width="31" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="17" customWidth="1"/>
+    <col min="7" max="7" width="45" customWidth="1"/>
+    <col min="8" max="8" width="45" customWidth="1"/>
+    <col min="9" max="9" width="45" customWidth="1"/>
+    <col min="10" max="10" width="45" customWidth="1"/>
+    <col min="11" max="11" width="28" customWidth="1"/>
+    <col min="12" max="12" width="18" customWidth="1"/>
+    <col min="13" max="13" width="24" customWidth="1"/>
+    <col min="14" max="14" width="45" customWidth="1"/>
+    <col min="15" max="15" width="40" customWidth="1"/>
+    <col min="16" max="16" width="31" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>id</t>
@@ -652,415 +354,422 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>958c2878-32c8-49d1-b5be-1c797362ae1f</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Two Sum</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>two-sum</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="7">
         <v>1000</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2" s="7">
         <v>256</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="9" t="inlineStr">
         <is>
           <t>Given an array of integers nums and an integer target, return indices of the two numbers such that they add up to target.</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="9" t="inlineStr">
         <is>
           <t>First line: n and target. Second line: n space-separated integers.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="9" t="inlineStr">
         <is>
           <t>Two space-separated 0-based indices.</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="9" t="inlineStr">
         <is>
           <t>2 &lt;= n &lt;= 10^4, -10^9 &lt;= nums[i] &lt;= 10^9</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>4 9
 2 7 11 15</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L2" s="3" t="inlineStr">
         <is>
           <t>0 1</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M2" s="3" t="inlineStr">
         <is>
           <t>array,hash-map</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N2" s="9" t="inlineStr">
         <is>
           <t>[{"index": 0, "input": "4 9\n2 7 11 15", "expected": "0 1"}, {"index": 1, "input": "3 6\n3 2 4", "expected": "1 2"}]</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="O2" s="3" t="inlineStr">
         <is>
           <t>7468653e-dfa4-492c-923f-1891feb76181</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="P2" s="5" t="inlineStr">
         <is>
           <t>2026-10-11T18:37:21.899250</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>9037c928-ceb7-437f-831e-dbc907bf05c0</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Fibonacci Sequence</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>fibonacci</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" s="6">
         <v>1000</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3" s="6">
         <v>256</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="8" t="inlineStr">
         <is>
           <t>Print the first n Fibonacci numbers starting from 0.</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="8" t="inlineStr">
         <is>
           <t>Single integer n.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="8" t="inlineStr">
         <is>
           <t>Space-separated Fibonacci numbers.</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="8" t="inlineStr">
         <is>
           <t>1 &lt;= n &lt;= 50</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr">
         <is>
           <t>0 1 1 2 3</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>dp,math</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N3" s="8" t="inlineStr">
         <is>
           <t>[{"index": 0, "input": "5", "expected": "0 1 1 2 3"}, {"index": 1, "input": "1", "expected": "0"}]</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>7468653e-dfa4-492c-923f-1891feb76181</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="P3" s="4" t="inlineStr">
         <is>
           <t>2026-10-11T18:37:21.899288</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>f1466f3a-5ea0-47a7-9b5c-1f9d453296e2</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Longest Common Subsequence</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>lcs</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="7">
         <v>2000</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="7">
         <v>256</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="9" t="inlineStr">
         <is>
           <t>Find the length of the longest common subsequence between two strings.</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="9" t="inlineStr">
         <is>
           <t>Two lines, each with a string.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" s="9" t="inlineStr">
         <is>
           <t>Single integer LCS length.</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J4" s="9" t="inlineStr">
         <is>
           <t>1 &lt;= |s|, |t| &lt;= 1000</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>abcde
 ace</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>dp,string</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N4" s="9" t="inlineStr">
         <is>
           <t>[{"index": 0, "input": "abcde\nace", "expected": "3"}, {"index": 1, "input": "abc\nabc", "expected": "3"}]</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="O4" s="3" t="inlineStr">
         <is>
           <t>7468653e-dfa4-492c-923f-1891feb76181</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="P4" s="5" t="inlineStr">
         <is>
           <t>2026-10-11T18:37:21.899319</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>03128b2e-50aa-469f-ba8a-bf7844e373fc</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Maximum Subarray</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>max-subarray</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" s="6">
         <v>1000</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="6">
         <v>256</v>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="8" t="inlineStr">
         <is>
           <t>Find the contiguous subarray with the largest sum (Kadanes Algorithm).</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="8" t="inlineStr">
         <is>
           <t>First line: n. Second line: n integers.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="8" t="inlineStr">
         <is>
           <t>Maximum subarray sum.</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J5" s="8" t="inlineStr">
         <is>
           <t>1 &lt;= n &lt;= 10^5</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>9
 -2 1 -3 4 -1 2 1 -5 4</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>dp,array</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N5" s="8" t="inlineStr">
         <is>
           <t>[{"index": 0, "input": "9\n-2 1 -3 4 -1 2 1 -5 4", "expected": "6"}, {"index": 1, "input": "1\n1", "expected": "1"}]</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>7468653e-dfa4-492c-923f-1891feb76181</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="P5" s="4" t="inlineStr">
         <is>
           <t>2026-10-11T18:37:21.899348</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>3483ceff-37dd-46a8-ad39-c885042063cf</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Binary Search</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>binary-search</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="7">
         <v>1000</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="7">
         <v>256</v>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="9" t="inlineStr">
         <is>
           <t>Find index of target in sorted array. Return -1 if not found.</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="9" t="inlineStr">
         <is>
           <t>Line 1: n and target. Line 2: n sorted integers.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" s="9" t="inlineStr">
         <is>
           <t>Index of target or -1.</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J6" s="9" t="inlineStr">
         <is>
           <t>1 &lt;= n &lt;= 10^4</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K6" s="3" t="inlineStr">
         <is>
           <t>6 9
 1 3 5 7 9 11</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="L6" s="3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M6" s="3" t="inlineStr">
         <is>
           <t>binary-search,array</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N6" s="9" t="inlineStr">
         <is>
           <t>[{"index": 0, "input": "6 9\n1 3 5 7 9 11", "expected": "4"}, {"index": 1, "input": "3 0\n1 2 3", "expected": "-1"}]</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="O6" s="3" t="inlineStr">
         <is>
           <t>7468653e-dfa4-492c-923f-1891feb76181</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="P6" s="5" t="inlineStr">
         <is>
           <t>2026-10-11T18:37:21.899376</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <autoFilter ref="A1:P6"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:J2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="40" customWidth="1"/>
+    <col min="2" max="2" width="23" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="31" customWidth="1"/>
+    <col min="5" max="5" width="31" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="7" max="7" width="40" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="9" max="9" width="40" customWidth="1"/>
+    <col min="10" max="10" width="31" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>id</t>
@@ -1112,71 +821,73 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>8b42b758-8fab-45a8-a820-2c4a83961131</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>CodeArena Round #1</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>round-1</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>2026-10-11T18:37:21.899405</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>2026-10-11T21:37:21.899405</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>ongoing</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Welcome to CodeArena! Compete, code, and climb the leaderboard.</t>
         </is>
       </c>
-      <c r="H2" t="b">
+      <c r="H2" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>7468653e-dfa4-492c-923f-1891feb76181</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="5" t="inlineStr">
         <is>
           <t>2026-10-11T18:37:21.899411</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <autoFilter ref="A1:J2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="40" customWidth="1"/>
+    <col min="2" max="2" width="40" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>id</t>
@@ -1203,136 +914,145 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>7fec38f0-9618-466e-a3cd-5e8382be53a9</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>8b42b758-8fab-45a8-a820-2c4a83961131</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>958c2878-32c8-49d1-b5be-1c797362ae1f</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="7">
         <v>1</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="7">
         <v>100</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>462732d8-5bcd-4847-802f-fce1044232a5</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>8b42b758-8fab-45a8-a820-2c4a83961131</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>9037c928-ceb7-437f-831e-dbc907bf05c0</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="6">
         <v>2</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" s="6">
         <v>100</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>df1f5df7-c692-4ba7-9a75-0fbd19d6a388</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>8b42b758-8fab-45a8-a820-2c4a83961131</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>f1466f3a-5ea0-47a7-9b5c-1f9d453296e2</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="7">
         <v>3</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="7">
         <v>200</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>516669c8-3194-43e5-825d-a06eed51ccc1</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>8b42b758-8fab-45a8-a820-2c4a83961131</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>03128b2e-50aa-469f-ba8a-bf7844e373fc</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="6">
         <v>4</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" s="6">
         <v>200</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>c33a6c30-ccf6-49a6-a40b-9e07f538b974</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>8b42b758-8fab-45a8-a820-2c4a83961131</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>3483ceff-37dd-46a8-ad39-c885042063cf</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="7">
         <v>5</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="7">
         <v>300</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <autoFilter ref="A1:E6"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:L7"/>
+  <cols>
+    <col min="1" max="1" width="40" customWidth="1"/>
+    <col min="2" max="2" width="40" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="40" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="45" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
+    <col min="11" max="11" width="31" customWidth="1"/>
+    <col min="12" max="12" width="45" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>id</t>
@@ -1394,30 +1114,31 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>2555937c-9a14-4841-b9e6-e7dd6c76eb00</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>7468653e-dfa4-492c-923f-1891feb76181</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>958c2878-32c8-49d1-b5be-1c797362ae1f</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="D2" s="3"/>
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
+      <c r="F2" s="9" t="inlineStr">
+        <is>
+          <t>
 import sys
 parts = sys.stdin.read().split()
 if parts:
@@ -1433,53 +1154,54 @@
 </t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>AC</t>
         </is>
       </c>
-      <c r="H2" t="n">
+      <c r="H2" s="7">
         <v>100</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2" s="7">
         <v>32</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2" s="7">
         <v>16</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" s="5" t="inlineStr">
         <is>
           <t>2026-10-11T18:45:50.377108</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L2" s="9" t="inlineStr">
         <is>
           <t>{"submission_id": "2555937c-9a14-4841-b9e6-e7dd6c76eb00", "verdict": "AC", "max_time_ms": 32, "max_memory_mb": 16, "tests_passed": 2, "tests_total": 2, "results": [{"test_index": 0, "verdict": "AC", "time_ms": 32}, {"test_index": 1, "verdict": "AC", "time_ms": 22}]}</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>5d92045a-eaa7-4c53-97e5-a19c28e418c4</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>216bb78f-92ec-46cb-a033-85bd1a01496e</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>f1466f3a-5ea0-47a7-9b5c-1f9d453296e2</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="D3" s="2"/>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>cpp</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="8" t="inlineStr">
         <is>
           <t>#include &lt;bits/stdc++.h&gt;
 using namespace std;
@@ -1491,53 +1213,54 @@
 }</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>WA</t>
         </is>
       </c>
-      <c r="H3" t="n">
+      <c r="H3" s="6">
         <v>0</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3" s="6">
         <v>2963</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3" s="6">
         <v>16</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" s="4" t="inlineStr">
         <is>
           <t>2026-10-11T18:48:22.954252</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L3" s="8" t="inlineStr">
         <is>
           <t>{"submission_id": "5d92045a-eaa7-4c53-97e5-a19c28e418c4", "verdict": "WA", "max_time_ms": 2963, "max_memory_mb": 16, "tests_passed": 0, "tests_total": 2, "results": [{"test_index": 0, "verdict": "WA", "time_ms": 2963, "actual": "", "expected": "3"}]}</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>c81e818c-c040-4aa8-9488-6246c5104f7b</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>216bb78f-92ec-46cb-a033-85bd1a01496e</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>958c2878-32c8-49d1-b5be-1c797362ae1f</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="D4" s="3"/>
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>cpp</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="9" t="inlineStr">
         <is>
           <t>#include &lt;bits/stdc++.h&gt;
 using namespace std;
@@ -1553,46 +1276,272 @@
 }</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>WA</t>
         </is>
       </c>
-      <c r="H4" t="n">
+      <c r="H4" s="7">
         <v>0</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4" s="7">
         <v>598</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4" s="7">
         <v>16</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K4" s="5" t="inlineStr">
         <is>
           <t>2026-10-11T18:50:54.054673</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="L4" s="9" t="inlineStr">
         <is>
           <t>{"submission_id": "c81e818c-c040-4aa8-9488-6246c5104f7b", "verdict": "WA", "max_time_ms": 598, "max_memory_mb": 16, "tests_passed": 0, "tests_total": 2, "results": [{"test_index": 0, "verdict": "WA", "time_ms": 598, "actual": "29", "expected": "0 1"}]}</t>
         </is>
       </c>
     </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>914ee822-9322-42c8-825f-87a5c4d29423</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>216bb78f-92ec-46cb-a033-85bd1a01496e</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>958c2878-32c8-49d1-b5be-1c797362ae1f</t>
+        </is>
+      </c>
+      <c r="D5" s="2"/>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>cpp</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>import sys
+def solve():
+  # Read all inputs from standard input
+  input_data = sys.stdin.read().split()
+  if not input_data:
+    return
+  # Parse n, target, and the array elements
+  n = int(input_data[0])
+  target = int(input_data[1])
+  nums = [int(x) for x in input_data[2 : 2 + n]]
+  # Hash map to store numbers and their indices
+  seen = {}
+  for i, num in enumerate(nums):
+    complement = target - num
+    if complement in seen:
+      print(f"{seen[complement]} {i}")
+      return
+    seen[num] = i
+if __name__ == "__main__":
+  solve()</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="H5" s="6">
+        <v>0</v>
+      </c>
+      <c r="I5" s="6">
+        <v>0</v>
+      </c>
+      <c r="J5" s="6">
+        <v>16</v>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-11T18:56:57.656923</t>
+        </is>
+      </c>
+      <c r="L5" s="8" t="inlineStr">
+        <is>
+          <t>{"submission_id": "914ee822-9322-42c8-825f-87a5c4d29423", "verdict": "CE", "max_time_ms": 0, "max_memory_mb": 16, "tests_passed": 0, "tests_total": 2, "results": [{"test_index": 0, "verdict": "CE", "error": "C:\\Users\\Pc\\AppData\\Local\\Temp\\judge_914ee822_190xe1nr\\solution.cpp:5:5: error: invalid preprocessing directive #Read\n   # Read all inputs from standard input\n     ^~~~\nC:\\Users\\Pc\\AppData\\Local\\Temp\\judge_914ee822_190xe1nr\\solution.cpp:10:5: error: invalid preprocessing directive #Parse\n   # Parse "}]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>54da94bc-e484-4dc4-97e2-d02e6b83d95c</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>216bb78f-92ec-46cb-a033-85bd1a01496e</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>958c2878-32c8-49d1-b5be-1c797362ae1f</t>
+        </is>
+      </c>
+      <c r="D6" s="3"/>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>cpp</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>#include &lt;iostream&gt;
+#include &lt;vector&gt;
+#include &lt;unordered_map&gt;
+using namespace std;
+int main() {
+    // Optimize standard I/O operations for speed
+    ios_base::sync_with_stdio(false);
+    cin.tie(NULL);
+    int n;
+    long long target;
+    if (!(cin &gt;&gt; n &gt;&gt; target)) return 0;
+    vector&lt;long long&gt; nums(n);
+    unordered_map&lt;long long, int&gt; seen;
+    for (int i = 0; i &lt; n; ++i) {
+        cin &gt;&gt; nums[i];
+    }
+    for (int i = 0; i &lt; n; ++i) {
+        long long complement = target - nums[i];
+        // Check if the complement exists in our map
+        if (seen.find(complement) != seen.end()) {
+            cout &lt;&lt; seen[complement] &lt;&lt; " " &lt;&lt; i &lt;&lt; "\n";
+            return 0;
+        }
+        // Store the current number and its index
+        seen[nums[i]] = i;
+    }
+    return 0;
+}</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="H6" s="7">
+        <v>100</v>
+      </c>
+      <c r="I6" s="7">
+        <v>1302</v>
+      </c>
+      <c r="J6" s="7">
+        <v>16</v>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-11T18:57:17.483034</t>
+        </is>
+      </c>
+      <c r="L6" s="9" t="inlineStr">
+        <is>
+          <t>{"submission_id": "54da94bc-e484-4dc4-97e2-d02e6b83d95c", "verdict": "AC", "max_time_ms": 1302, "max_memory_mb": 16, "tests_passed": 2, "tests_total": 2, "results": [{"test_index": 0, "verdict": "AC", "time_ms": 1302}, {"test_index": 1, "verdict": "AC", "time_ms": 1222}]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>20b67e7b-be3c-4713-b9ea-1ada972fd17a</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>7468653e-dfa4-492c-923f-1891feb76181</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>958c2878-32c8-49d1-b5be-1c797362ae1f</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>8b42b758-8fab-45a8-a820-2c4a83961131</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>import sys
+def solve():
+    parts = sys.stdin.read().split()
+    if not parts:
+        return
+    n = int(parts[0])
+    target = int(parts[1])
+    nums = [int(x) for x in parts[2:2+n]]
+    seen = {}
+    for i, x in enumerate(nums):
+        diff = target - x
+        if diff in seen:
+            print(f"{seen[diff]} {i}")
+            return
+        seen[x] = i
+solve()</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="H7" s="6">
+        <v>100</v>
+      </c>
+      <c r="I7" s="6">
+        <v>179</v>
+      </c>
+      <c r="J7" s="6">
+        <v>16</v>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-16T19:28:02Z</t>
+        </is>
+      </c>
+      <c r="L7" s="8" t="inlineStr">
+        <is>
+          <t>{"submission_id":"20b67e7b-be3c-4713-b9ea-1ada972fd17a","verdict":"AC","max_time_ms":179,"max_memory_mb":16,"tests_passed":2,"tests_total":2,"results":[{"test_index":0,"verdict":"AC","time_ms":179},{"test_index":1,"verdict":"AC","time_ms":106}]}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <autoFilter ref="A1:L7"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:H2"/>
+  <cols>
+    <col min="1" max="1" width="40" customWidth="1"/>
+    <col min="2" max="2" width="40" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="20" customWidth="1"/>
+    <col min="7" max="7" width="25" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>id</t>
@@ -1634,21 +1583,58 @@
         </is>
       </c>
     </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>199869b9-ae9d-49b9-a3f9-b17a294d85ac</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>8b42b758-8fab-45a8-a820-2c4a83961131</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>7468653e-dfa4-492c-923f-1891feb76181</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="E2" s="7">
+        <v>100</v>
+      </c>
+      <c r="F2" s="7">
+        <v>1</v>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-16T19:28:03Z</t>
+        </is>
+      </c>
+      <c r="H2" s="7">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <autoFilter ref="A1:H2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:D2"/>
+  <cols>
+    <col min="1" max="1" width="40" customWidth="1"/>
+    <col min="2" max="2" width="40" customWidth="1"/>
+    <col min="3" max="3" width="31" customWidth="1"/>
+    <col min="4" max="4" width="31" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>token</t>
@@ -1670,51 +1656,29 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>qpVE-rIEP8rlYV84eHYk8ipurHzEX3FcrVOhA6ctzek</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>7468653e-dfa4-492c-923f-1891feb76181</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2026-10-11T18:45:50.319159</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-10-18T18:45:50.319137</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>r4ypTixtbaM5mpQIwVidUoZPJUTOqg0eUPKdk_ZbSDw</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>216bb78f-92ec-46cb-a033-85bd1a01496e</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>2026-10-11T18:52:12.583568</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>2026-10-18T18:52:12.583509</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <autoFilter ref="A1:D2"/>
 </worksheet>
 </file>